--- a/artfynd/A 15676-2022 artfynd.xlsx
+++ b/artfynd/A 15676-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15676-2022 artfynd.xlsx
+++ b/artfynd/A 15676-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80434248</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539001.1153827201</v>
+        <v>539001</v>
       </c>
       <c r="R2" t="n">
-        <v>6326726.882684378</v>
+        <v>6326727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,19 +759,9 @@
           <t>2019-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,12 +792,7 @@
         <v>101554499</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -856,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538922.8265964031</v>
+        <v>538923</v>
       </c>
       <c r="R3" t="n">
-        <v>6326597.887899579</v>
+        <v>6326598</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,19 +869,9 @@
           <t>2022-05-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
